--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N95_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N95_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.10199303608139</v>
+        <v>1.966573868363225</v>
       </c>
       <c r="D2" t="n">
-        <v>78.50392296781494</v>
+        <v>12.75688748226993</v>
       </c>
       <c r="E2" t="n">
-        <v>15.06339576563889</v>
+        <v>2.44780181191632</v>
       </c>
       <c r="F2" t="n">
-        <v>22.29302263916959</v>
+        <v>3.622616178865059</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.32395056034453</v>
+        <v>8.177641966055987</v>
       </c>
       <c r="D3" t="n">
-        <v>20.5</v>
+        <v>3.33125</v>
       </c>
       <c r="E3" t="n">
-        <v>15.06339576563889</v>
+        <v>2.44780181191632</v>
       </c>
       <c r="F3" t="n">
-        <v>22.29302263916959</v>
+        <v>3.622616178865059</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.65029474719319</v>
+        <v>7.580672896418893</v>
       </c>
       <c r="D4" t="n">
-        <v>22.47220505424423</v>
+        <v>3.651733321314688</v>
       </c>
       <c r="E4" t="n">
-        <v>15.06339576563889</v>
+        <v>2.44780181191632</v>
       </c>
       <c r="F4" t="n">
-        <v>22.29302263916959</v>
+        <v>3.622616178865059</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.46623098590774</v>
+        <v>4.950762535210007</v>
       </c>
       <c r="D5" t="n">
-        <v>59.37562625518697</v>
+        <v>9.648539266467884</v>
       </c>
       <c r="E5" t="n">
-        <v>15.06339576563889</v>
+        <v>2.44780181191632</v>
       </c>
       <c r="F5" t="n">
-        <v>22.29302263916959</v>
+        <v>3.622616178865059</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.68440466227133</v>
+        <v>1.086215757619091</v>
       </c>
       <c r="D6" t="n">
-        <v>14.37717443805996</v>
+        <v>2.336290846184744</v>
       </c>
       <c r="E6" t="n">
-        <v>15.06339576563889</v>
+        <v>2.44780181191632</v>
       </c>
       <c r="F6" t="n">
-        <v>22.29302263916959</v>
+        <v>3.622616178865059</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.30139068748415</v>
+        <v>3.786475986716175</v>
       </c>
       <c r="D7" t="n">
-        <v>24.4829829973959</v>
+        <v>3.978484737076833</v>
       </c>
       <c r="E7" t="n">
-        <v>15.06339576563889</v>
+        <v>2.44780181191632</v>
       </c>
       <c r="F7" t="n">
-        <v>22.29302263916959</v>
+        <v>3.622616178865059</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.34082039143231</v>
+        <v>4.11788331360775</v>
       </c>
       <c r="D8" t="n">
-        <v>25.56621162060683</v>
+        <v>4.15450938834861</v>
       </c>
       <c r="E8" t="n">
-        <v>15.06339576563889</v>
+        <v>2.44780181191632</v>
       </c>
       <c r="F8" t="n">
-        <v>22.29302263916959</v>
+        <v>3.622616178865059</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
